--- a/Result/profitability/1537.xlsx
+++ b/Result/profitability/1537.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.1275</v>
+        <v>1.94125</v>
       </c>
       <c r="N2" t="n">
-        <v>20.43875</v>
+        <v>19.86</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>1.68</v>
+        <v>1.6025</v>
       </c>
       <c r="N3" t="n">
-        <v>18.86625</v>
+        <v>18.78375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>1.45875</v>
+        <v>1.38875</v>
       </c>
       <c r="N4" t="n">
-        <v>17.705</v>
+        <v>17.4125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0125</v>
+        <v>1.095</v>
       </c>
       <c r="N5" t="n">
-        <v>15.91875</v>
+        <v>15.66875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8424999999999999</v>
+        <v>0.8225</v>
       </c>
       <c r="N6" t="n">
-        <v>14.26</v>
+        <v>14.34375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.76</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.64375</v>
       </c>
       <c r="N7" t="n">
-        <v>14.445</v>
+        <v>14.5575</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.52</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7212499999999999</v>
+        <v>0.6950000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.50875</v>
+        <v>15.425</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1724</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1385</v>
+      </c>
+      <c r="E75" t="n">
+        <v>338</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>191</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>203</v>
+      </c>
+      <c r="K75" t="n">
+        <v>156</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.23375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.71125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.09952606635071093</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6699999999999982</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03302119270576631</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09250693802035148</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
